--- a/assets/bidtree.xlsx
+++ b/assets/bidtree.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trambert/projects/Bidding/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94BB5E8-3C15-454B-B265-9FA366A5E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9ED318D-83C2-D144-BFA9-F0B0245727BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="37680" windowHeight="21000" xr2:uid="{C67589D8-C51A-194F-8A92-BFA7BFE68D55}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4037" uniqueCount="707">
   <si>
     <t>Enchère</t>
   </si>
@@ -2080,9 +2080,6 @@
     <t>A,n,p</t>
   </si>
   <si>
-    <t>M,5,4</t>
-  </si>
-  <si>
     <t>par,5,4</t>
   </si>
   <si>
@@ -2092,12 +2089,6 @@
     <t>C,5,4</t>
   </si>
   <si>
-    <t>M,5,3</t>
-  </si>
-  <si>
-    <t>M,5,5</t>
-  </si>
-  <si>
     <t>par,5,5</t>
   </si>
   <si>
@@ -2122,15 +2113,6 @@
     <t>K,3,4</t>
   </si>
   <si>
-    <t>m,3,5</t>
-  </si>
-  <si>
-    <t>m,3,6</t>
-  </si>
-  <si>
-    <t>m,3,7</t>
-  </si>
-  <si>
     <t>par,3,5</t>
   </si>
   <si>
@@ -2143,9 +2125,6 @@
     <t>K,3,5</t>
   </si>
   <si>
-    <t>M,4,4</t>
-  </si>
-  <si>
     <t>Couleur fittée, et nbr mini de cartes fittées du partenaire, et du joueur</t>
   </si>
   <si>
@@ -2171,6 +2150,18 @@
   </si>
   <si>
     <t>- -</t>
+  </si>
+  <si>
+    <t>par,3,6</t>
+  </si>
+  <si>
+    <t>par,3,7</t>
+  </si>
+  <si>
+    <t>6E -</t>
+  </si>
+  <si>
+    <t>7E -</t>
   </si>
 </sst>
 </file>
@@ -2780,7 +2771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E999B0E-BCB1-0548-9F4F-0A962A7A4ADD}">
-  <dimension ref="A1:AE382"/>
+  <dimension ref="A1:AE384"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="17" customWidth="1"/>
@@ -4528,7 +4519,7 @@
         <v>25</v>
       </c>
       <c r="Z29" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA29" s="5"/>
       <c r="AB29" s="5"/>
@@ -4585,7 +4576,7 @@
         <v>19</v>
       </c>
       <c r="Z30" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AA30" s="5">
         <v>1</v>
@@ -4646,7 +4637,7 @@
         <v>19</v>
       </c>
       <c r="Z31" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA31" s="5">
         <v>1</v>
@@ -4888,7 +4879,7 @@
         <v>72</v>
       </c>
       <c r="Z35" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA35" s="5"/>
       <c r="AB35" s="5"/>
@@ -4953,7 +4944,7 @@
         <v>254</v>
       </c>
       <c r="Z36" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA36" s="5"/>
       <c r="AB36" s="5"/>
@@ -5063,7 +5054,7 @@
         <v>40</v>
       </c>
       <c r="Z38" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA38" s="5"/>
       <c r="AB38" s="5"/>
@@ -5116,7 +5107,7 @@
         <v>25</v>
       </c>
       <c r="Z39" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AA39" s="5">
         <v>1</v>
@@ -5342,7 +5333,7 @@
         <v>44</v>
       </c>
       <c r="Z43" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA43" s="5">
         <v>1</v>
@@ -5403,7 +5394,7 @@
         <v>56</v>
       </c>
       <c r="Z44" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AA44" s="5"/>
       <c r="AB44" s="5"/>
@@ -5460,7 +5451,7 @@
         <v>58</v>
       </c>
       <c r="Z45" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AA45" s="5">
         <v>1</v>
@@ -5523,7 +5514,7 @@
         <v>60</v>
       </c>
       <c r="Z46" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AA46" s="5">
         <v>1</v>
@@ -5586,7 +5577,7 @@
         <v>61</v>
       </c>
       <c r="Z47" s="5" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="AA47" s="5">
         <v>1</v>
@@ -5649,7 +5640,7 @@
         <v>62</v>
       </c>
       <c r="Z48" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AA48" s="5">
         <v>1</v>
@@ -6640,7 +6631,7 @@
         <v>40</v>
       </c>
       <c r="Z65" s="5" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="AA65" s="5"/>
       <c r="AB65" s="5"/>
@@ -6707,7 +6698,7 @@
         <v>12</v>
       </c>
       <c r="Z66" s="5" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="AA66" s="5"/>
       <c r="AB66" s="5"/>
@@ -6774,7 +6765,7 @@
         <v>74</v>
       </c>
       <c r="Z67" s="5" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AA67" s="5"/>
       <c r="AB67" s="5"/>
@@ -7346,7 +7337,7 @@
         <v>19</v>
       </c>
       <c r="Z77" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AA77" s="5"/>
       <c r="AB77" s="5"/>
@@ -7399,7 +7390,7 @@
         <v>74</v>
       </c>
       <c r="Z78" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AA78" s="5"/>
       <c r="AB78" s="5"/>
@@ -7452,7 +7443,7 @@
         <v>12</v>
       </c>
       <c r="Z79" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA79" s="5"/>
       <c r="AB79" s="5"/>
@@ -7505,7 +7496,7 @@
         <v>291</v>
       </c>
       <c r="Z80" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA80" s="5"/>
       <c r="AB80" s="5"/>
@@ -7560,7 +7551,7 @@
         <v>40</v>
       </c>
       <c r="Z81" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA81" s="5"/>
       <c r="AB81" s="5"/>
@@ -7613,7 +7604,7 @@
         <v>25</v>
       </c>
       <c r="Z82" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AA82" s="5">
         <v>1</v>
@@ -7733,7 +7724,7 @@
         <v>323</v>
       </c>
       <c r="Z84" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA84" s="5"/>
       <c r="AB84" s="5"/>
@@ -7790,7 +7781,7 @@
         <v>44</v>
       </c>
       <c r="Z85" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA85" s="5">
         <v>1</v>
@@ -7851,7 +7842,7 @@
         <v>56</v>
       </c>
       <c r="Z86" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AA86" s="5"/>
       <c r="AB86" s="5"/>
@@ -7908,7 +7899,7 @@
         <v>58</v>
       </c>
       <c r="Z87" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AA87" s="5">
         <v>1</v>
@@ -7971,7 +7962,7 @@
         <v>60</v>
       </c>
       <c r="Z88" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AA88" s="5">
         <v>1</v>
@@ -8034,7 +8025,7 @@
         <v>61</v>
       </c>
       <c r="Z89" s="5" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="AA89" s="5">
         <v>1</v>
@@ -8097,7 +8088,7 @@
         <v>62</v>
       </c>
       <c r="Z90" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AA90" s="5">
         <v>1</v>
@@ -9172,7 +9163,7 @@
         <v>66</v>
       </c>
       <c r="Z109" s="5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="AA109" s="5"/>
       <c r="AB109" s="5"/>
@@ -9227,7 +9218,7 @@
         <v>323</v>
       </c>
       <c r="Z110" s="5" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="AA110" s="5"/>
       <c r="AB110" s="5"/>
@@ -9282,7 +9273,7 @@
         <v>324</v>
       </c>
       <c r="Z111" s="5" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="AA111" s="5"/>
       <c r="AB111" s="5"/>
@@ -9335,7 +9326,7 @@
         <v>25</v>
       </c>
       <c r="Z112" s="5" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="AA112" s="5">
         <v>1</v>
@@ -9392,7 +9383,7 @@
         <v>65</v>
       </c>
       <c r="Z113" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA113" s="5"/>
       <c r="AB113" s="5"/>
@@ -9445,7 +9436,7 @@
         <v>25</v>
       </c>
       <c r="Z114" s="5" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="AA114" s="5">
         <v>1</v>
@@ -9504,7 +9495,7 @@
         <v>397</v>
       </c>
       <c r="Z115" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA115" s="5"/>
       <c r="AB115" s="5"/>
@@ -9559,7 +9550,7 @@
         <v>44</v>
       </c>
       <c r="Z116" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA116" s="5">
         <v>1</v>
@@ -9618,7 +9609,7 @@
         <v>61</v>
       </c>
       <c r="Z117" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AA117" s="5"/>
       <c r="AB117" s="5"/>
@@ -9673,7 +9664,7 @@
         <v>255</v>
       </c>
       <c r="Z118" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="AA118" s="5">
         <v>1</v>
@@ -9744,7 +9735,7 @@
         <v>324</v>
       </c>
       <c r="Z119" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA119" s="5"/>
       <c r="AB119" s="5"/>
@@ -9799,7 +9790,7 @@
         <v>72</v>
       </c>
       <c r="Z120" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA120" s="5">
         <v>1</v>
@@ -10143,7 +10134,7 @@
         <v>40</v>
       </c>
       <c r="Z126" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA126" s="5"/>
       <c r="AB126" s="5"/>
@@ -10196,7 +10187,7 @@
         <v>25</v>
       </c>
       <c r="Z127" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA127" s="5">
         <v>1</v>
@@ -10373,7 +10364,7 @@
         <v>56</v>
       </c>
       <c r="Z130" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AA130" s="5"/>
       <c r="AB130" s="5"/>
@@ -10430,7 +10421,7 @@
         <v>255</v>
       </c>
       <c r="Z131" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="AA131" s="5">
         <v>1</v>
@@ -10501,7 +10492,7 @@
         <v>324</v>
       </c>
       <c r="Z132" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA132" s="5"/>
       <c r="AB132" s="5"/>
@@ -10566,7 +10557,7 @@
         <v>61</v>
       </c>
       <c r="Z133" s="5" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="AA133" s="5"/>
       <c r="AB133" s="5"/>
@@ -10631,7 +10622,7 @@
         <v>62</v>
       </c>
       <c r="Z134" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AA134" s="5"/>
       <c r="AB134" s="5"/>
@@ -10688,7 +10679,7 @@
         <v>254</v>
       </c>
       <c r="Z135" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA135" s="5">
         <v>1</v>
@@ -11740,7 +11731,7 @@
         <v>19</v>
       </c>
       <c r="Z153" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AA153" s="5"/>
       <c r="AB153" s="5"/>
@@ -11793,7 +11784,7 @@
         <v>74</v>
       </c>
       <c r="Z154" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AA154" s="5"/>
       <c r="AB154" s="5"/>
@@ -11846,7 +11837,7 @@
         <v>12</v>
       </c>
       <c r="Z155" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA155" s="5"/>
       <c r="AB155" s="5"/>
@@ -11899,7 +11890,7 @@
         <v>291</v>
       </c>
       <c r="Z156" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA156" s="5"/>
       <c r="AB156" s="5"/>
@@ -12512,7 +12503,7 @@
         <v>12</v>
       </c>
       <c r="Z167" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA167" s="5"/>
       <c r="AB167" s="5"/>
@@ -12565,7 +12556,7 @@
         <v>291</v>
       </c>
       <c r="Z168" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="AA168" s="5"/>
       <c r="AB168" s="5"/>
@@ -12620,7 +12611,7 @@
         <v>40</v>
       </c>
       <c r="Z169" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="AA169" s="5"/>
       <c r="AB169" s="5"/>
@@ -12732,7 +12723,7 @@
         <v>56</v>
       </c>
       <c r="Z171" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="AA171" s="5"/>
       <c r="AB171" s="5"/>
@@ -12787,7 +12778,7 @@
         <v>25</v>
       </c>
       <c r="Z172" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA172" s="5">
         <v>1</v>
@@ -12907,7 +12898,7 @@
         <v>254</v>
       </c>
       <c r="Z174" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA174" s="5"/>
       <c r="AB174" s="5"/>
@@ -13064,7 +13055,7 @@
         <v>12</v>
       </c>
       <c r="Z177" s="5" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="AA177" s="5"/>
       <c r="AB177" s="5"/>
@@ -13308,7 +13299,7 @@
         <v>25</v>
       </c>
       <c r="Z181" s="5" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="AA181" s="5"/>
       <c r="AB181" s="5" t="s">
@@ -20900,7 +20891,7 @@
         <v>51</v>
       </c>
       <c r="Z317" s="40" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AA317" s="40"/>
       <c r="AB317" s="40"/>
@@ -20961,7 +20952,7 @@
         <v>56</v>
       </c>
       <c r="Z318" s="40" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AA318" s="40"/>
       <c r="AB318" s="40" t="s">
@@ -21022,7 +21013,7 @@
         <v>62</v>
       </c>
       <c r="Z319" s="5" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AA319" s="5">
         <v>1</v>
@@ -21085,7 +21076,7 @@
         <v>397</v>
       </c>
       <c r="Z320" s="5" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA320" s="5">
         <v>1</v>
@@ -21272,7 +21263,7 @@
         <v>74</v>
       </c>
       <c r="Z323" s="40" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AA323" s="40">
         <v>1</v>
@@ -21333,7 +21324,7 @@
         <v>291</v>
       </c>
       <c r="Z324" s="40" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA324" s="40">
         <v>1</v>
@@ -21394,7 +21385,7 @@
         <v>58</v>
       </c>
       <c r="Z325" s="40" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AA325" s="40">
         <v>1</v>
@@ -21457,7 +21448,7 @@
         <v>60</v>
       </c>
       <c r="Z326" s="40" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA326" s="40">
         <v>1</v>
@@ -21520,7 +21511,7 @@
         <v>397</v>
       </c>
       <c r="Z327" s="5" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="AA327" s="5"/>
       <c r="AB327" s="5" t="s">
@@ -21579,7 +21570,7 @@
         <v>62</v>
       </c>
       <c r="Z328" s="5" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA328" s="5"/>
       <c r="AB328" s="5" t="s">
@@ -21638,7 +21629,7 @@
         <v>58</v>
       </c>
       <c r="Z329" s="5" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AA329" s="5">
         <v>1</v>
@@ -21699,7 +21690,7 @@
         <v>60</v>
       </c>
       <c r="Z330" s="5" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="AA330" s="5">
         <v>1</v>
@@ -21760,7 +21751,7 @@
         <v>61</v>
       </c>
       <c r="Z331" s="5" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="AA331" s="5">
         <v>1</v>
@@ -22539,7 +22530,7 @@
         <v>397</v>
       </c>
       <c r="Z346" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AC346" s="5" t="s">
         <v>584</v>
@@ -22581,7 +22572,7 @@
         <v>62</v>
       </c>
       <c r="Z347" s="1" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="AC347" s="5" t="s">
         <v>584</v>
@@ -22683,7 +22674,7 @@
         <v>56</v>
       </c>
       <c r="Z350" s="1" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="AD350" s="5">
         <v>26</v>
@@ -22721,7 +22712,7 @@
         <v>397</v>
       </c>
       <c r="Z351" s="1" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AD351" s="5">
         <v>26</v>
@@ -22759,7 +22750,7 @@
         <v>62</v>
       </c>
       <c r="Z352" s="1" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AD352" s="5">
         <v>26</v>
@@ -22806,7 +22797,7 @@
         <v>58</v>
       </c>
       <c r="Z353" s="5" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AC353" s="5" t="s">
         <v>59</v>
@@ -22856,7 +22847,7 @@
         <v>58</v>
       </c>
       <c r="Z354" s="5" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AC354" s="5" t="s">
         <v>59</v>
@@ -22906,7 +22897,7 @@
         <v>60</v>
       </c>
       <c r="Z355" s="5" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AC355" s="5" t="s">
         <v>59</v>
@@ -22956,7 +22947,7 @@
         <v>60</v>
       </c>
       <c r="Z356" s="5" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AC356" s="5" t="s">
         <v>59</v>
@@ -23006,7 +22997,7 @@
         <v>61</v>
       </c>
       <c r="Z357" s="5" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AC357" s="5" t="s">
         <v>59</v>
@@ -23213,7 +23204,9 @@
       <c r="AD362" s="5">
         <v>26</v>
       </c>
-      <c r="AE362" s="5"/>
+      <c r="AE362" s="5" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="363" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A363" s="13">
@@ -23796,7 +23789,7 @@
       <c r="P378" s="5"/>
       <c r="Q378" s="5"/>
       <c r="R378" s="7" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="S378" s="45"/>
       <c r="T378" s="45"/>
@@ -23818,11 +23811,13 @@
       <c r="AD378" s="5">
         <v>64</v>
       </c>
-      <c r="AE378" s="5"/>
+      <c r="AE378" s="5" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="379" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A379" s="13">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B379" s="5" t="s">
         <v>665</v>
@@ -23857,7 +23852,9 @@
       <c r="X379" s="5"/>
       <c r="Y379" s="5"/>
       <c r="Z379" s="5"/>
-      <c r="AA379" s="5"/>
+      <c r="AA379" s="5">
+        <v>1</v>
+      </c>
       <c r="AB379" s="5"/>
       <c r="AC379" s="5"/>
       <c r="AD379" s="5">
@@ -23869,7 +23866,7 @@
     </row>
     <row r="380" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A380" s="13">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>665</v>
@@ -23904,7 +23901,9 @@
       <c r="X380" s="5"/>
       <c r="Y380" s="5"/>
       <c r="Z380" s="5"/>
-      <c r="AA380" s="5"/>
+      <c r="AA380" s="5">
+        <v>1</v>
+      </c>
       <c r="AB380" s="5"/>
       <c r="AC380" s="5"/>
       <c r="AD380" s="5">
@@ -23916,7 +23915,7 @@
     </row>
     <row r="381" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A381" s="13">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>665</v>
@@ -23951,17 +23950,21 @@
       <c r="X381" s="5"/>
       <c r="Y381" s="5"/>
       <c r="Z381" s="5"/>
-      <c r="AA381" s="5"/>
+      <c r="AA381" s="5">
+        <v>1</v>
+      </c>
       <c r="AB381" s="5"/>
       <c r="AC381" s="5"/>
-      <c r="AD381" s="5"/>
+      <c r="AD381" s="5">
+        <v>64</v>
+      </c>
       <c r="AE381" s="5" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="382" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A382" s="13">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B382" s="5" t="s">
         <v>665</v>
@@ -23975,7 +23978,68 @@
       <c r="V382" s="5" t="s">
         <v>670</v>
       </c>
+      <c r="AD382" s="5">
+        <v>64</v>
+      </c>
       <c r="AE382" s="5" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="383" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A383" s="13">
+        <v>381</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="R383" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="X383" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y383" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB383" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD383" s="5">
+        <v>64</v>
+      </c>
+      <c r="AE383" s="5" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="384" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A384" s="13">
+        <v>382</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="R384" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="X384" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y384" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB384" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD384" s="5">
+        <v>64</v>
+      </c>
+      <c r="AE384" s="5" t="s">
         <v>671</v>
       </c>
     </row>
@@ -24449,13 +24513,13 @@
         <v>209</v>
       </c>
       <c r="C31" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="D31" t="s">
         <v>678</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
